--- a/files/Menus Listed.xlsx
+++ b/files/Menus Listed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb03e65629f95fa6/Documents/01 Personal/01 Web Development/01 Sites/11 C2C Rides/C2C_Rides/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E11E8F9-EF5F-48C4-9482-CBCD652D9544}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32430C34-F246-4303-9460-EB60CE113B1E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
   </bookViews>
   <sheets>
     <sheet name="Hotel 1 - Menu Info" sheetId="5" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="Hotel 4 - Menu Info" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Hotel 1 - Menu Info'!$B$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Hotel 2 - Menu Info'!$B$1:$I$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Hotel 3 - Menu Info'!$B$1:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Hotel 4 - Menu Info'!$B$1:$J$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Hotel 1 - Menu Info'!$B$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Hotel 2 - Menu Info'!$B$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Hotel 3 - Menu Info'!$B$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Hotel 4 - Menu Info'!$B$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="123">
   <si>
     <t>David Olney</t>
   </si>
@@ -382,13 +382,67 @@
   </si>
   <si>
     <t>Hotel: The Lion</t>
+  </si>
+  <si>
+    <t>Jane Olney</t>
+  </si>
+  <si>
+    <t>Kevin Marriott</t>
+  </si>
+  <si>
+    <t>Beer battered cod, chips, peas - £18.50</t>
+  </si>
+  <si>
+    <t>Heather Marriott</t>
+  </si>
+  <si>
+    <t>Paul Nathan</t>
+  </si>
+  <si>
+    <t>vegetarian</t>
+  </si>
+  <si>
+    <t>Crumble of the week, with custard and pouring cream - £10.50</t>
+  </si>
+  <si>
+    <t>No Garlic please</t>
+  </si>
+  <si>
+    <t>Classic Dishes: Hunters Chicken Burger - Crispy chicken, bacon, cheese &amp; BBQ sauce with coleslaw, hand cut chips - £14.95</t>
+  </si>
+  <si>
+    <t>Special Dishes: Pan Roasted Wild Local Seabass - white wine &amp; mussels sauce - £21.95</t>
+  </si>
+  <si>
+    <t>Classic Dishes: Vegetable Lasagne (V) - Dressed leaves, chips &amp; garlic bread - £14.95</t>
+  </si>
+  <si>
+    <t>Double Chocolate Brownie - Warm Brownie served with signature chocolate sauce &amp; vanilla ice cream - £7.95</t>
+  </si>
+  <si>
+    <t>vegetarian desert please, these are not labelled</t>
+  </si>
+  <si>
+    <t>Cumberland Sausage &amp; Mash - With vegetables and gravy - £17.95</t>
+  </si>
+  <si>
+    <t>Cheese Board - With biscuits, fruit and chutney - £12.95</t>
+  </si>
+  <si>
+    <t>Beetroot Hummus (VG) - With warm flatbread - £7.95</t>
+  </si>
+  <si>
+    <t>Instead of mushy peas can I have salad</t>
+  </si>
+  <si>
+    <t>Leek, Mushroom &amp; Lentil Shepherds Pie (VG) - With mashed potato and vegetables - £16.95</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,8 +474,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,6 +508,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -547,41 +618,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-0.14996795556505021"/>
       </left>
@@ -594,11 +630,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -646,37 +711,65 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="50">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -713,7 +806,9 @@
         <left style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
         <top style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </top>
@@ -740,6 +835,421 @@
         <left style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
         <right/>
         <top style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
@@ -749,6 +1259,160 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -899,13 +1563,6 @@
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -934,6 +1591,13 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -944,58 +1608,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
         <vertical style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </vertical>
@@ -1177,519 +1789,8 @@
     <dxf>
       <border>
         <top style="thin">
-          <color rgb="FFD9D9D9"/>
+          <color theme="0" tint="-0.14996795556505021"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1716,6 +1817,32 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1730,31 +1857,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:G25" totalsRowShown="0" headerRowDxfId="38" dataDxfId="48" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
-  <autoFilter ref="B5:G25" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="39"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H25" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" headerRowBorderDxfId="34" tableBorderDxfId="35" totalsRowBorderDxfId="33">
-  <autoFilter ref="B5:H25" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:H24" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+  <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1764,21 +1873,45 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{E6C72533-73F5-43F8-B0CD-008DE01142AB}" name="Meal preparation comments" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H24" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
+  <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I25" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
-  <autoFilter ref="B5:I25" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I24" totalsRowShown="0" headerRowDxfId="26" dataDxfId="9" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+  <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1789,22 +1922,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I25" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="B5:I25" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I24" totalsRowShown="0" headerRowDxfId="22" dataDxfId="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+  <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1815,14 +1948,14 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2145,42 +2278,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BE3EC9-DCB1-4B11-A224-FE491FDA9B83}">
-  <dimension ref="B1:O41"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P40"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="63.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="41.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="50.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.77734375" style="1"/>
-    <col min="13" max="13" width="45.109375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.77734375" style="1"/>
+    <col min="8" max="8" width="20.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="1" customWidth="1"/>
+    <col min="12" max="12" width="63.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="45.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="3" spans="2:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="K3" s="4"/>
+    </row>
+    <row r="5" spans="2:15" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>33</v>
       </c>
@@ -2199,26 +2337,29 @@
       <c r="G5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>0</v>
       </c>
@@ -2235,8 +2376,9 @@
       <c r="G6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="7" t="str" cm="1">
-        <f t="array" ref="I6:J8">_xlfn.LET(
+      <c r="H6" s="16"/>
+      <c r="J6" s="7" t="str" cm="1">
+        <f t="array" ref="J6:K8">_xlfn.LET(
     _xlpm.rng, tblHotel13[Starter],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Starter") * (_xlpm.u &lt;&gt; "")),
@@ -2244,11 +2386,11 @@
 )</f>
         <v>Creamy Garlic Mushrooms, Sourdough bread £8.50</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <v>4</v>
       </c>
-      <c r="K6" s="7" t="str" cm="1">
-        <f t="array" ref="K6:L13">_xlfn.LET(
+      <c r="L6" s="7" t="str" cm="1">
+        <f t="array" ref="L6:M14">_xlfn.LET(
     _xlpm.rng, tblHotel13[Main],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
@@ -2256,11 +2398,11 @@
 )</f>
         <v>Cheese &amp; Potato Pie with chips, sticky red cabbage, gravy - £17.50</v>
       </c>
-      <c r="L6" s="9">
+      <c r="M6" s="9">
         <v>1</v>
       </c>
-      <c r="M6" s="7" t="str" cm="1">
-        <f t="array" ref="M6:N8">_xlfn.LET(
+      <c r="N6" s="7" t="str" cm="1">
+        <f t="array" ref="N6:O9">_xlfn.LET(
     _xlpm.rng, tblHotel13[Dessert],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Dessert") * (_xlpm.u &lt;&gt; "")),
@@ -2268,11 +2410,11 @@
 )</f>
         <v>Chocolate Brownie, with Ice Cream - £8.50</v>
       </c>
-      <c r="N6" s="9">
+      <c r="O6" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>16</v>
       </c>
@@ -2289,26 +2431,27 @@
       <c r="G7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="H7" s="16"/>
+      <c r="J7" s="7" t="str">
         <v>Classic Prawn Cocktail, Marie Rose Sauce, Rye Bread £11</v>
       </c>
-      <c r="J7" s="9">
+      <c r="K7" s="9">
         <v>1</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="L7" s="7" t="str">
         <v>Steak &amp; Ale Pie with mash, sticky red cabbage, gravy - £17.50</v>
       </c>
-      <c r="L7" s="9">
+      <c r="M7" s="9">
         <v>2</v>
       </c>
-      <c r="M7" s="7" t="str">
+      <c r="N7" s="7" t="str">
         <v>Sticky Toffee Pudding with Custard - £9</v>
       </c>
-      <c r="N7" s="9">
+      <c r="O7" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
@@ -2327,26 +2470,27 @@
       <c r="G8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="H8" s="16"/>
+      <c r="J8" s="7" t="str">
         <v>Hummus, flatbread, and olives £7.50</v>
       </c>
-      <c r="J8" s="9">
+      <c r="K8" s="9">
         <v>1</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="L8" s="7" t="str">
         <v>Sweet potato roulade with a tomato &amp; herb sauce, and seasonal veg - £16.50</v>
       </c>
-      <c r="L8" s="9">
+      <c r="M8" s="9">
+        <v>2</v>
+      </c>
+      <c r="N8" s="7" t="str">
+        <v>Sweet Potato cake, caramel sauce - £8.50</v>
+      </c>
+      <c r="O8" s="9">
         <v>1</v>
       </c>
-      <c r="M8" s="7" t="str">
-        <v>Sweet Potato cake, caramel sauce - £8.50</v>
-      </c>
-      <c r="N8" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:15" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="14" t="s">
         <v>4</v>
       </c>
@@ -2363,18 +2507,23 @@
       <c r="G9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="7" t="str">
+      <c r="H9" s="16"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="7" t="str">
         <v>Chicken Pie with mash, sticky red cabbage, gravy - £17.50</v>
       </c>
-      <c r="L9" s="9">
+      <c r="M9" s="9">
+        <v>2</v>
+      </c>
+      <c r="N9" s="7" t="str">
+        <v>Crumble of the week, with custard and pouring cream - £10.50</v>
+      </c>
+      <c r="O9" s="9">
         <v>1</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>19</v>
       </c>
@@ -2391,18 +2540,19 @@
       <c r="G10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="7" t="str">
+      <c r="H10" s="16"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="7" t="str">
         <v>Homemade beef lasagne, Garlic bread - £18</v>
       </c>
-      <c r="L10" s="9">
+      <c r="M10" s="9">
         <v>2</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N10" s="7"/>
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="14" t="s">
         <v>11</v>
       </c>
@@ -2419,18 +2569,19 @@
       <c r="G11" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="7" t="str">
+      <c r="H11" s="16"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="7" t="str">
         <v>Steak Rump served with tomato, mushroom, chips, garlic butter sauce - £24</v>
       </c>
-      <c r="L11" s="9">
+      <c r="M11" s="9">
         <v>1</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="N11" s="7"/>
+      <c r="O11" s="9"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
         <v>13</v>
       </c>
@@ -2447,18 +2598,19 @@
       <c r="G12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="7" t="str">
+      <c r="H12" s="16"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="7" t="str">
         <v>Steak &amp; Ale Pie with chips, sticky red cabbage, gravy - £17.50</v>
       </c>
-      <c r="L12" s="9">
-        <v>2</v>
-      </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M12" s="9">
+        <v>3</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="O12" s="9"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
@@ -2475,18 +2627,19 @@
       <c r="G13" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="7" t="str">
+      <c r="H13" s="16"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="7" t="str">
         <v>Steak Rump served with tomato, mushroom, chips, peppercorn sauce - £24</v>
       </c>
-      <c r="L13" s="9">
+      <c r="M13" s="9">
         <v>1</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="N13" s="7"/>
+      <c r="O13" s="9"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>21</v>
       </c>
@@ -2503,14 +2656,19 @@
       <c r="G14" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="H14" s="16"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="7" t="str">
+        <v>Beer battered cod, chips, peas - £18.50</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
         <v>42</v>
       </c>
@@ -2527,14 +2685,15 @@
       <c r="G15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="H15" s="16"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>24</v>
       </c>
@@ -2551,14 +2710,15 @@
       <c r="G16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H16" s="16"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="9"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>9</v>
       </c>
@@ -2575,14 +2735,15 @@
       <c r="G17" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H17" s="16"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>15</v>
       </c>
@@ -2599,129 +2760,170 @@
       <c r="G18" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
+      <c r="E19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="16"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B21" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="E21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="14"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="16"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="14"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="O28" s="6"/>
-    </row>
-    <row r="29" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I29" s="1"/>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I40" s="1"/>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="9:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -2730,16 +2932,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED18A305-6A6D-4E08-8BDC-3A0A86BECE38}">
-  <dimension ref="B1:P41"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P40"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="63.33203125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="41.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="48.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="42.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="1" customWidth="1"/>
@@ -2765,7 +2971,7 @@
       </c>
       <c r="K3" s="4"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>33</v>
       </c>
@@ -2784,7 +2990,7 @@
       <c r="G5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="19" t="s">
         <v>44</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -2823,7 +3029,7 @@
       <c r="G6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="21"/>
+      <c r="H6" s="18"/>
       <c r="J6" s="7" t="str" cm="1">
         <f t="array" ref="J6:K8">_xlfn.LET(
     _xlpm.rng, tblHotel134[Starter],
@@ -2858,7 +3064,7 @@
         <v>Sticky Toffee Pudding with Custard</v>
       </c>
       <c r="O6" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -2878,7 +3084,7 @@
       <c r="G7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="17" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="7" t="str">
@@ -2891,13 +3097,13 @@
         <v>Beer battered Cod &amp; Chips served with chips, mushy peas, lemon wedge &amp; tartare sauce</v>
       </c>
       <c r="M7" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N7" s="7" t="str">
         <v>Cheesecake with Mix Berries Compote</v>
       </c>
       <c r="O7" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
@@ -2919,7 +3125,7 @@
       <c r="G8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="17" t="s">
         <v>52</v>
       </c>
       <c r="J8" s="7" t="str">
@@ -2932,7 +3138,7 @@
         <v>Tadka Dal (Red Lentil Curry) A flavorful and hearty dish, made with red lentils, simmered in mild spices, tempered with onions, garlic and cumin. Served with saffron flavored basmati rice &amp; Poppadum</v>
       </c>
       <c r="M8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="9"/>
@@ -2954,14 +3160,14 @@
       <c r="G9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="H9" s="17"/>
       <c r="J9" s="7"/>
       <c r="K9" s="9"/>
       <c r="L9" s="7" t="str">
         <v>Seafood Tagliatelle simmered in Bisque with prawns, squids &amp; mussels served with lemon, Urfa Chilli, chives &amp; Parmesan</v>
       </c>
       <c r="M9" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="9"/>
@@ -2983,7 +3189,7 @@
       <c r="G10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="20"/>
+      <c r="H10" s="17"/>
       <c r="J10" s="7"/>
       <c r="K10" s="9"/>
       <c r="L10" s="7" t="str">
@@ -3012,7 +3218,7 @@
       <c r="G11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="20"/>
+      <c r="H11" s="17"/>
       <c r="J11" s="7"/>
       <c r="K11" s="9"/>
       <c r="L11" s="7"/>
@@ -3037,7 +3243,7 @@
       <c r="G12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="17"/>
       <c r="J12" s="7"/>
       <c r="K12" s="9"/>
       <c r="L12" s="7"/>
@@ -3062,7 +3268,7 @@
       <c r="G13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="20"/>
+      <c r="H13" s="17"/>
       <c r="J13" s="7"/>
       <c r="K13" s="9"/>
       <c r="L13" s="7"/>
@@ -3087,7 +3293,7 @@
       <c r="G14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="17" t="s">
         <v>57</v>
       </c>
       <c r="J14" s="7"/>
@@ -3114,7 +3320,7 @@
       <c r="G15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="20"/>
+      <c r="H15" s="17"/>
       <c r="J15" s="7"/>
       <c r="K15" s="9"/>
       <c r="L15" s="7"/>
@@ -3139,7 +3345,7 @@
       <c r="G16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="20"/>
+      <c r="H16" s="17"/>
       <c r="J16" s="7"/>
       <c r="K16" s="9"/>
       <c r="L16" s="7"/>
@@ -3164,7 +3370,7 @@
       <c r="G17" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="20"/>
+      <c r="H17" s="17"/>
       <c r="J17" s="7"/>
       <c r="K17" s="9"/>
       <c r="L17" s="7"/>
@@ -3189,7 +3395,7 @@
       <c r="G18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="20"/>
+      <c r="H18" s="17"/>
       <c r="J18" s="2"/>
       <c r="K18" s="10"/>
       <c r="L18" s="2"/>
@@ -3197,14 +3403,24 @@
       <c r="N18" s="2"/>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
+    <row r="19" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="20"/>
+      <c r="E19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="17"/>
       <c r="J19" s="2"/>
       <c r="K19" s="10"/>
       <c r="L19" s="2"/>
@@ -3212,14 +3428,26 @@
       <c r="N19" s="2"/>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
+    <row r="20" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="20"/>
+      <c r="E20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>112</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="10"/>
       <c r="L20" s="2"/>
@@ -3227,23 +3455,45 @@
       <c r="N20" s="2"/>
       <c r="O20" s="10"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
+    <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="20"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="20"/>
+      <c r="E21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="14"/>
@@ -3252,7 +3502,7 @@
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="16"/>
-      <c r="H23" s="20"/>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="14"/>
@@ -3261,19 +3511,18 @@
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
-      <c r="H24" s="20"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="22"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="P28" s="6"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
     </row>
     <row r="29" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="J29" s="1"/>
@@ -3283,14 +3532,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
+    <row r="30" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -3299,7 +3541,14 @@
     <row r="36" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+    </row>
     <row r="40" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3307,19 +3556,11 @@
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="10:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="P40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3328,12 +3569,705 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{315E00E8-B705-4EBE-A801-E2DC2C3EDF0C}">
-  <dimension ref="B1:Q41"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:Q40"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="43.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="63.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" customWidth="1"/>
+    <col min="13" max="13" width="50.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="1"/>
+    <col min="15" max="15" width="45.109375" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="2:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="5" spans="2:16" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="K6" s="7" t="str" cm="1">
+        <f t="array" ref="K6:L8">_xlfn.LET(
+    _xlpm.rng, tblHotel1345[Starter],
+    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
+    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Starter") * (_xlpm.u &lt;&gt; "")),
+    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
+)</f>
+        <v>Creamy Garlic Mushrooms (V) - Crusty bread &amp; butter - £7.95</v>
+      </c>
+      <c r="L6" s="9">
+        <v>4</v>
+      </c>
+      <c r="M6" s="7" t="str" cm="1">
+        <f t="array" ref="M6:N16">_xlfn.LET(
+    _xlpm.rng, tblHotel1345[Main],
+    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
+    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
+    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
+)</f>
+        <v>Light Bites: Peppered Steak Loaded Fries - With slow cooked steak in a creamy peppercorn sauce - £12.95</v>
+      </c>
+      <c r="N6" s="9">
+        <v>3</v>
+      </c>
+      <c r="O6" s="7" t="str" cm="1">
+        <f t="array" ref="O6:P9">_xlfn.LET(
+    _xlpm.rng, tblHotel1345[Dessert],
+    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
+    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Dessert") * (_xlpm.u &lt;&gt; "")),
+    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
+)</f>
+        <v>Banoffee Belgian Waffle - Belgian Wafle topped with bananas, signature toffee sauce &amp; honeycomb ice cream - £7.95</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="K7" s="7" t="str">
+        <v>Thai Bass Fishcakes - With sweet chilli &amp; coriander salad - £8.95</v>
+      </c>
+      <c r="L7" s="9">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7" t="str">
+        <v>Classic Dishes: Beef Lasagne - Dressed leaves, chips &amp; garlic bread - £14.95</v>
+      </c>
+      <c r="N7" s="9">
+        <v>2</v>
+      </c>
+      <c r="O7" s="7" t="str">
+        <v>Lemon Posset - Creamy Lemon dessert with shortbread biscuit and berries - £7.95</v>
+      </c>
+      <c r="P7" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="K8" s="7" t="str">
+        <v>Shredded Duck Bon Bons - Hoisin mayo &amp; sticky dressing - £8.95</v>
+      </c>
+      <c r="L8" s="9">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7" t="str">
+        <v>Special Dishes: Pan Fried Salmon - With tomatoes, garlic, chilli &amp; coriander - £19.95</v>
+      </c>
+      <c r="N8" s="9">
+        <v>2</v>
+      </c>
+      <c r="O8" s="7" t="str">
+        <v>Eton Mess - Crushed meringue, mixed fruit &amp; fresh cream - £7.95</v>
+      </c>
+      <c r="P8" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="24"/>
+      <c r="H9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="7" t="str">
+        <v>Classic Dishes: Nanhoron Tikka Curry - Chicken, Served with rice, naan, mango chutney - £15.95</v>
+      </c>
+      <c r="N9" s="9">
+        <v>2</v>
+      </c>
+      <c r="O9" s="7" t="str">
+        <v>Double Chocolate Brownie - Warm Brownie served with signature chocolate sauce &amp; vanilla ice cream - £7.95</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="7" t="str">
+        <v>Classic Dishes: Steak &amp; Local Ale Pie - With puff pastry top &amp; served with peas and chips - £15.95</v>
+      </c>
+      <c r="N10" s="9">
+        <v>1</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="9"/>
+    </row>
+    <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="7" t="str">
+        <v>Classic Dishes: House Burger - Double beef, cheese, pickles, lettuce, burger sauce, coleslaw, hand-cut chips - £14.95</v>
+      </c>
+      <c r="N11" s="9">
+        <v>1</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="9"/>
+    </row>
+    <row r="12" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="H12" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="7" t="str">
+        <v>Special Dishes: Chicken Supreme - stuffed with bacon &amp; cheese, wrapped in parma ham served on a bed of creamed leeks - £18.95</v>
+      </c>
+      <c r="N12" s="9">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="9"/>
+    </row>
+    <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7" t="str">
+        <v>Special Dishes: Crispy 1/2 Roast Duck - With orange sauce - £21.95</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7"/>
+      <c r="P13" s="9"/>
+    </row>
+    <row r="14" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="7" t="str">
+        <v>Classic Dishes: Hunters Chicken Burger - Crispy chicken, bacon, cheese &amp; BBQ sauce with coleslaw, hand cut chips - £14.95</v>
+      </c>
+      <c r="N14" s="9">
+        <v>1</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="9"/>
+    </row>
+    <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="7" t="str">
+        <v>Special Dishes: Pan Roasted Wild Local Seabass - white wine &amp; mussels sauce - £21.95</v>
+      </c>
+      <c r="N15" s="9">
+        <v>2</v>
+      </c>
+      <c r="O15" s="7"/>
+      <c r="P15" s="9"/>
+    </row>
+    <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="26"/>
+      <c r="H16" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="7" t="str">
+        <v>Classic Dishes: Vegetable Lasagne (V) - Dressed leaves, chips &amp; garlic bread - £14.95</v>
+      </c>
+      <c r="N16" s="9">
+        <v>1</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="9"/>
+    </row>
+    <row r="17" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B17" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="26"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="9"/>
+    </row>
+    <row r="18" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="26"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="26"/>
+      <c r="H19" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="26"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B20" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="10"/>
+    </row>
+    <row r="21" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B21" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="26"/>
+    </row>
+    <row r="22" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q27" s="6"/>
+    </row>
+    <row r="28" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1190403F-5DA9-4FF4-BFB7-23DC06F291A3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q40"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" customWidth="1"/>
     <col min="5" max="5" width="43.5546875" style="1" customWidth="1"/>
     <col min="6" max="7" width="63.33203125" style="1" customWidth="1"/>
@@ -3347,14 +4281,20 @@
     <col min="16" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B1" s="3" t="s">
-        <v>103</v>
+    <row r="1" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="28"/>
+      <c r="B1" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="3" spans="2:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+    </row>
+    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="28"/>
+      <c r="B3" s="30" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="4"/>
@@ -3363,29 +4303,33 @@
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+    </row>
+    <row r="5" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="21" t="s">
         <v>44</v>
       </c>
       <c r="K5" s="5" t="s">
@@ -3407,102 +4351,102 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
+    <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="21"/>
+      <c r="E6" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="24"/>
       <c r="K6" s="7" t="str" cm="1">
-        <f t="array" ref="K6:L8">_xlfn.LET(
-    _xlpm.rng, tblHotel1345[Starter],
+        <f t="array" ref="K6:L12">_xlfn.LET(
+    _xlpm.rng, tblHotel13456[Starter],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Starter") * (_xlpm.u &lt;&gt; "")),
     _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
 )</f>
-        <v>Creamy Garlic Mushrooms (V) - Crusty bread &amp; butter - £7.95</v>
+        <v>Potato Skins (V) – With cheese, garlic sauce and crispy onions - £7.95</v>
       </c>
       <c r="L6" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" s="7" t="str" cm="1">
-        <f t="array" ref="M6:N13">_xlfn.LET(
-    _xlpm.rng, tblHotel1345[Main],
+        <f t="array" ref="M6:N17">_xlfn.LET(
+    _xlpm.rng, tblHotel13456[Main],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
     _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
 )</f>
-        <v>Light Bites: Peppered Steak Loaded Fries - With slow cooked steak in a creamy peppercorn sauce - £12.95</v>
+        <v>Steak &amp; Ale Pie - With chips and vegetables - £18.95</v>
       </c>
       <c r="N6" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" s="7" t="str" cm="1">
-        <f t="array" ref="O6:P8">_xlfn.LET(
-    _xlpm.rng, tblHotel1345[Dessert],
+        <f t="array" ref="O6:P11">_xlfn.LET(
+    _xlpm.rng, tblHotel13456[Dessert],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Dessert") * (_xlpm.u &lt;&gt; "")),
     _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
 )</f>
-        <v>Banoffee Belgian Waffle - Belgian Wafle topped with bananas, signature toffee sauce &amp; honeycomb ice cream - £7.95</v>
+        <v>Tiramisu - Coffee, sponge and cream dessert - £6.95</v>
       </c>
       <c r="P6" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="K7" s="7" t="str">
+        <v>Soup of the Day (V) – With bread and butter - £6.95</v>
+      </c>
+      <c r="L7" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="20"/>
-      <c r="K7" s="7" t="str">
-        <v>Thai Bass Fishcakes - With sweet chilli &amp; coriander salad - £8.95</v>
-      </c>
-      <c r="L7" s="9">
+      <c r="M7" s="7" t="str">
+        <v>Chicken Supreme with Chasseur Sauce - With mashed potato and vegetables - £18.95</v>
+      </c>
+      <c r="N7" s="9">
         <v>3</v>
       </c>
-      <c r="M7" s="7" t="str">
-        <v>Classic Dishes: Beef Lasagne - Dressed leaves, chips &amp; garlic bread - £14.95</v>
-      </c>
-      <c r="N7" s="9">
-        <v>2</v>
-      </c>
       <c r="O7" s="7" t="str">
-        <v>Lemon Posset - Creamy Lemon dessert with shortbread biscuit and berries - £7.95</v>
+        <v>Coconut &amp; Vanilla Panna Cotta - With pineapple salsa - £7.95</v>
       </c>
       <c r="P7" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -3511,151 +4455,183 @@
       <c r="D8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="E8" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="20"/>
+      <c r="I8" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="K8" s="7" t="str">
-        <v>Shredded Duck Bon Bons - Hoisin mayo &amp; sticky dressing - £8.95</v>
+        <v>Pheasant &amp; Mushroom Pate - With toasted sourdough - £8.95</v>
       </c>
       <c r="L8" s="9">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7" t="str">
+        <v>Thai Green Vegetable Curry (V) - With steamed rice and flatbread - £15.95</v>
+      </c>
+      <c r="N8" s="9">
         <v>1</v>
       </c>
-      <c r="M8" s="7" t="str">
-        <v>Special Dishes: Pan Fried Salmon - With tomatoes, garlic, chilli &amp; coriander - £19.95</v>
-      </c>
-      <c r="N8" s="9">
+      <c r="O8" s="7" t="str">
+        <v>Rhubarb &amp; Stem Ginger Crumble (V) - With custard - £7.95</v>
+      </c>
+      <c r="P8" s="9">
         <v>2</v>
       </c>
-      <c r="O8" s="7" t="str">
-        <v>Eton Mess - Crushed meringue, mixed fruit &amp; fresh cream - £7.95</v>
-      </c>
-      <c r="P8" s="9">
+    </row>
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="K9" s="7" t="str">
+        <v>Chicken Caesar Croquettes - With salad and Parmesan - £7.95</v>
+      </c>
+      <c r="L9" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="9"/>
       <c r="M9" s="7" t="str">
-        <v>Classic Dishes: Nanhoron Tikka Curry - Chicken, Served with rice, naan, mango chutney - £15.95</v>
+        <v>Cod &amp; Lemon Fishcakes - With pea and bacon salad - £18.95</v>
       </c>
       <c r="N9" s="9">
         <v>2</v>
       </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="14" t="s">
+      <c r="O9" s="7" t="str">
+        <v>Rhubarb &amp; Stem Ginger Crumble (V) - With vanilla ice cream - £7.95</v>
+      </c>
+      <c r="P9" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="20"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="9"/>
+      <c r="E10" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="K10" s="7" t="str">
+        <v>Spicy Meatballs – With a roast tomato sauce, Parmesan and rocket - £8.95</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1</v>
+      </c>
       <c r="M10" s="7" t="str">
-        <v>Classic Dishes: Steak &amp; Local Ale Pie - With puff pastry top &amp; served with peas and chips - £15.95</v>
+        <v>Lamb Hot Pot Pie &amp; Mint Gravy - With mashed potato and vegetables - £18.95</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
       </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="9"/>
-    </row>
-    <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="14" t="s">
+      <c r="O10" s="7" t="str">
+        <v>Penderyn Whisky &amp; Chocolate Basque Cheesecake - With Chantilly cream - £7.95</v>
+      </c>
+      <c r="P10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9"/>
+      <c r="F11" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="K11" s="7" t="str">
+        <v>Cod &amp; Lemon Fishcake - With parsley sauce - £8.95</v>
+      </c>
+      <c r="L11" s="9">
+        <v>1</v>
+      </c>
       <c r="M11" s="7" t="str">
-        <v>Classic Dishes: House Burger - Double beef, cheese, pickles, lettuce, burger sauce, coleslaw, hand-cut chips - £14.95</v>
+        <v>Lamb Hot Pot Pie &amp; Mint Gravy - With chips and vegetables - £18.95</v>
       </c>
       <c r="N11" s="9">
+        <v>2</v>
+      </c>
+      <c r="O11" s="7" t="str">
+        <v>Cheese Board - With biscuits, fruit and chutney - £12.95</v>
+      </c>
+      <c r="P11" s="9">
         <v>1</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="14" t="s">
+    </row>
+    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="20"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="9"/>
+      <c r="F12" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="H12" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="K12" s="7" t="str">
+        <v>Beetroot Hummus (VG) - With warm flatbread - £7.95</v>
+      </c>
+      <c r="L12" s="9">
+        <v>1</v>
+      </c>
       <c r="M12" s="7" t="str">
-        <v>Special Dishes: Chicken Supreme - stuffed with bacon &amp; cheese, wrapped in parma ham served on a bed of creamed leeks - £18.95</v>
+        <v>Steak &amp; Ale Pie - With mashed potato and vegetables - £18.95</v>
       </c>
       <c r="N12" s="9">
         <v>1</v>
@@ -3663,159 +4639,183 @@
       <c r="O12" s="7"/>
       <c r="P12" s="9"/>
     </row>
-    <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="14" t="s">
+    <row r="13" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="15"/>
-      <c r="E13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16" t="s">
+      <c r="E13" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="26"/>
       <c r="K13" s="7"/>
       <c r="L13" s="9"/>
       <c r="M13" s="7" t="str">
-        <v>Special Dishes: Crispy 1/2 Roast Duck - With orange sauce - £21.95</v>
+        <v>Scampi &amp; Chips - With mushy peas and tartare sauce - £17.95</v>
       </c>
       <c r="N13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="9"/>
     </row>
-    <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="14" t="s">
+    <row r="14" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="20"/>
+      <c r="E14" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="26"/>
       <c r="K14" s="7"/>
       <c r="L14" s="9"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="9"/>
+      <c r="M14" s="7" t="str">
+        <v>The Bull’s Buffalo Chicken Burger - With smoked cheese, ranch slaw and fries - £17.95</v>
+      </c>
+      <c r="N14" s="9">
+        <v>1</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B15" s="14" t="s">
+    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="20"/>
+      <c r="F15" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="26"/>
       <c r="K15" s="7"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="M15" s="7" t="str">
+        <v>Oven-Roasted Pheasant &amp; Black Pudding Bon Bon - With potato fondant, vegetables and whisky sauce - £18.95</v>
+      </c>
+      <c r="N15" s="9">
+        <v>1</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="9"/>
     </row>
-    <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="15"/>
-      <c r="E16" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="20"/>
+      <c r="E16" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="26"/>
       <c r="K16" s="7"/>
       <c r="L16" s="9"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="9"/>
+      <c r="M16" s="7" t="str">
+        <v>Cumberland Sausage &amp; Mash - With vegetables and gravy - £17.95</v>
+      </c>
+      <c r="N16" s="9">
+        <v>1</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="9"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="15"/>
-      <c r="E17" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16" t="s">
+      <c r="E17" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="20"/>
+      <c r="I17" s="26"/>
       <c r="K17" s="7"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="M17" s="7" t="str">
+        <v>Leek, Mushroom &amp; Lentil Shepherds Pie (VG) - With mashed potato and vegetables - £16.95</v>
+      </c>
+      <c r="N17" s="9">
+        <v>1</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="9"/>
     </row>
-    <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="14" t="s">
+    <row r="18" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="15" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="15"/>
-      <c r="E18" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="20"/>
+      <c r="E18" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="26"/>
       <c r="K18" s="2"/>
       <c r="L18" s="10"/>
       <c r="M18" s="2"/>
@@ -3823,15 +4823,25 @@
       <c r="O18" s="2"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
+    <row r="19" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="20"/>
+      <c r="E19" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="26"/>
+      <c r="H19" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="26"/>
       <c r="K19" s="2"/>
       <c r="L19" s="10"/>
       <c r="M19" s="2"/>
@@ -3839,15 +4849,27 @@
       <c r="O19" s="2"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
+    <row r="20" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B20" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="20"/>
+      <c r="E20" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>112</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="10"/>
       <c r="M20" s="2"/>
@@ -3855,58 +4877,80 @@
       <c r="O20" s="2"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
+    <row r="21" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B21" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="20"/>
+      <c r="E21" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="26"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="20"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B24" s="14"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="20"/>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="22"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="Q28" s="6"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="27"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q27" s="6"/>
+    </row>
+    <row r="28" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="K29" s="1"/>
@@ -3916,14 +4960,7 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
+    <row r="30" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -3932,7 +4969,14 @@
     <row r="36" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
     <row r="40" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -3940,692 +4984,11 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="Q40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1190403F-5DA9-4FF4-BFB7-23DC06F291A3}">
-  <dimension ref="B1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5546875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="63.33203125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="41.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="1" customWidth="1"/>
-    <col min="13" max="13" width="50.77734375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="1"/>
-    <col min="15" max="15" width="45.109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.77734375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="3" spans="2:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="K3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="K6" s="7" t="str" cm="1">
-        <f t="array" ref="K6:L11">_xlfn.LET(
-    _xlpm.rng, tblHotel13456[Starter],
-    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
-    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Starter") * (_xlpm.u &lt;&gt; "")),
-    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
-)</f>
-        <v>Potato Skins (V) – With cheese, garlic sauce and crispy onions - £7.95</v>
-      </c>
-      <c r="L6" s="9">
-        <v>2</v>
-      </c>
-      <c r="M6" s="7" t="str" cm="1">
-        <f t="array" ref="M6:N15">_xlfn.LET(
-    _xlpm.rng, tblHotel13456[Main],
-    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
-    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
-    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
-)</f>
-        <v>Steak &amp; Ale Pie - With chips and vegetables - £18.95</v>
-      </c>
-      <c r="N6" s="9">
-        <v>1</v>
-      </c>
-      <c r="O6" s="7" t="str" cm="1">
-        <f t="array" ref="O6:P10">_xlfn.LET(
-    _xlpm.rng, tblHotel13456[Dessert],
-    _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
-    _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Dessert") * (_xlpm.u &lt;&gt; "")),
-    _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
-)</f>
-        <v>Tiramisu - Coffee, sponge and cream dessert - £6.95</v>
-      </c>
-      <c r="P6" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="20"/>
-      <c r="K7" s="7" t="str">
-        <v>Soup of the Day (V) – With bread and butter - £6.95</v>
-      </c>
-      <c r="L7" s="9">
-        <v>1</v>
-      </c>
-      <c r="M7" s="7" t="str">
-        <v>Chicken Supreme with Chasseur Sauce - With mashed potato and vegetables - £18.95</v>
-      </c>
-      <c r="N7" s="9">
-        <v>2</v>
-      </c>
-      <c r="O7" s="7" t="str">
-        <v>Coconut &amp; Vanilla Panna Cotta - With pineapple salsa - £7.95</v>
-      </c>
-      <c r="P7" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="7" t="str">
-        <v>Pheasant &amp; Mushroom Pate - With toasted sourdough - £8.95</v>
-      </c>
-      <c r="L8" s="9">
-        <v>2</v>
-      </c>
-      <c r="M8" s="7" t="str">
-        <v>Thai Green Vegetable Curry (V) - With steamed rice and flatbread - £15.95</v>
-      </c>
-      <c r="N8" s="9">
-        <v>1</v>
-      </c>
-      <c r="O8" s="7" t="str">
-        <v>Rhubarb &amp; Stem Ginger Crumble (V) - With custard - £7.95</v>
-      </c>
-      <c r="P8" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="K9" s="7" t="str">
-        <v>Chicken Caesar Croquettes - With salad and Parmesan - £7.95</v>
-      </c>
-      <c r="L9" s="9">
-        <v>1</v>
-      </c>
-      <c r="M9" s="7" t="str">
-        <v>Cod &amp; Lemon Fishcakes - With pea and bacon salad - £18.95</v>
-      </c>
-      <c r="N9" s="9">
-        <v>2</v>
-      </c>
-      <c r="O9" s="7" t="str">
-        <v>Rhubarb &amp; Stem Ginger Crumble (V) - With vanilla ice cream - £7.95</v>
-      </c>
-      <c r="P9" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="20"/>
-      <c r="K10" s="7" t="str">
-        <v>Spicy Meatballs – With a roast tomato sauce, Parmesan and rocket - £8.95</v>
-      </c>
-      <c r="L10" s="9">
-        <v>1</v>
-      </c>
-      <c r="M10" s="7" t="str">
-        <v>Lamb Hot Pot Pie &amp; Mint Gravy - With mashed potato and vegetables - £18.95</v>
-      </c>
-      <c r="N10" s="9">
-        <v>1</v>
-      </c>
-      <c r="O10" s="7" t="str">
-        <v>Penderyn Whisky &amp; Chocolate Basque Cheesecake - With Chantilly cream - £7.95</v>
-      </c>
-      <c r="P10" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="7" t="str">
-        <v>Cod &amp; Lemon Fishcake - With parsley sauce - £8.95</v>
-      </c>
-      <c r="L11" s="9">
-        <v>1</v>
-      </c>
-      <c r="M11" s="7" t="str">
-        <v>Lamb Hot Pot Pie &amp; Mint Gravy - With chips and vegetables - £18.95</v>
-      </c>
-      <c r="N11" s="9">
-        <v>2</v>
-      </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="20"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="7" t="str">
-        <v>Steak &amp; Ale Pie - With mashed potato and vegetables - £18.95</v>
-      </c>
-      <c r="N12" s="9">
-        <v>1</v>
-      </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="20"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7" t="str">
-        <v>Scampi &amp; Chips - With mushy peas and tartare sauce - £17.95</v>
-      </c>
-      <c r="N13" s="9">
-        <v>1</v>
-      </c>
-      <c r="O13" s="7"/>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="20"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="7" t="str">
-        <v>The Bull’s Buffalo Chicken Burger - With smoked cheese, ranch slaw and fries - £17.95</v>
-      </c>
-      <c r="N14" s="9">
-        <v>1</v>
-      </c>
-      <c r="O14" s="7"/>
-      <c r="P14" s="9"/>
-    </row>
-    <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="20"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="7" t="str">
-        <v>Oven-Roasted Pheasant &amp; Black Pudding Bon Bon - With potato fondant, vegetables and whisky sauce - £18.95</v>
-      </c>
-      <c r="N15" s="9">
-        <v>1</v>
-      </c>
-      <c r="O15" s="7"/>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="20"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="9"/>
-    </row>
-    <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="20"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="9"/>
-    </row>
-    <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I18" s="20"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="10"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="20"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="10"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="20"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="10"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="20"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="20"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="20"/>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="22"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="Q28" s="6"/>
-    </row>
-    <row r="29" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="11:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/files/Menus Listed.xlsx
+++ b/files/Menus Listed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb03e65629f95fa6/Documents/01 Personal/01 Web Development/01 Sites/11 C2C Rides/C2C_Rides/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32430C34-F246-4303-9460-EB60CE113B1E}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{828D102A-55D7-4261-93B7-DF7B56032332}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
   </bookViews>
   <sheets>
     <sheet name="Hotel 1 - Menu Info" sheetId="5" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="121">
   <si>
     <t>David Olney</t>
   </si>
@@ -202,12 +202,6 @@
   </si>
   <si>
     <t>Meal preparation comments</t>
-  </si>
-  <si>
-    <t>Crispy onion &amp; corn bites served with mango mole</t>
-  </si>
-  <si>
-    <t>Lion’s Hot Chicken Burger with gherkins, balsamic onions, Tomato, Lettuce and Chef’ special sauce</t>
   </si>
   <si>
     <t>Beer battered Cod &amp; Chips served with chips, mushy peas, lemon wedge &amp; tartare sauce</t>
@@ -663,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -744,13 +738,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,16 +746,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
+          <fgColor indexed="64"/>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -995,270 +973,6 @@
         <horizontal style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1285,53 +999,13 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -1635,6 +1309,29 @@
         <bottom style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
         <vertical style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
         </vertical>
@@ -1822,6 +1519,296 @@
       <border>
         <bottom style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
         </bottom>
       </border>
     </dxf>
@@ -1862,7 +1849,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:H24" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:H24" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1873,20 +1860,20 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{E6C72533-73F5-43F8-B0CD-008DE01142AB}" name="Meal preparation comments" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{E6C72533-73F5-43F8-B0CD-008DE01142AB}" name="Meal preparation comments" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H24" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H24" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1897,20 +1884,20 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I24" totalsRowShown="0" headerRowDxfId="26" dataDxfId="9" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I24" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1922,21 +1909,21 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I24" totalsRowShown="0" headerRowDxfId="22" dataDxfId="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I24" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1948,14 +1935,14 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2359,7 +2346,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>0</v>
       </c>
@@ -2770,7 +2757,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>39</v>
@@ -2795,7 +2782,7 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>39</v>
@@ -2805,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>3</v>
@@ -2820,7 +2807,7 @@
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>39</v>
@@ -2839,13 +2826,13 @@
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>10</v>
@@ -2854,7 +2841,7 @@
         <v>28</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2957,7 +2944,7 @@
   <sheetData>
     <row r="1" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C1" s="3"/>
     </row>
@@ -3021,38 +3008,38 @@
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="G6" s="16" t="s">
         <v>46</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>3</v>
       </c>
       <c r="H6" s="18"/>
       <c r="J6" s="7" t="str" cm="1">
-        <f t="array" ref="J6:K8">_xlfn.LET(
+        <f t="array" ref="J6:K7">_xlfn.LET(
     _xlpm.rng, tblHotel134[Starter],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Starter") * (_xlpm.u &lt;&gt; "")),
     _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
 )</f>
-        <v>Crispy onion &amp; corn bites served with mango mole</v>
+        <v>Chef’s Soup of the Day</v>
       </c>
       <c r="K6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="7" t="str" cm="1">
-        <f t="array" ref="L6:M10">_xlfn.LET(
+        <f t="array" ref="L6:M9">_xlfn.LET(
     _xlpm.rng, tblHotel134[Main],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
     _xlfn.HSTACK(_xlpm.uClean, COUNTIF(_xlpm.rng, _xlpm.uClean))
 )</f>
-        <v>Lion’s Hot Chicken Burger with gherkins, balsamic onions, Tomato, Lettuce and Chef’ special sauce</v>
+        <v>Beer battered Cod &amp; Chips served with chips, mushy peas, lemon wedge &amp; tartare sauce</v>
       </c>
       <c r="M6" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N6" s="7" t="str" cm="1">
         <f t="array" ref="N6:O7">_xlfn.LET(
@@ -3064,7 +3051,7 @@
         <v>Sticky Toffee Pudding with Custard</v>
       </c>
       <c r="O6" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -3079,25 +3066,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>49</v>
-      </c>
       <c r="J7" s="7" t="str">
-        <v>Chef’s Soup of the Day</v>
+        <v>Lightly fried whitebait served with burnt lemon &amp; tartar dip</v>
       </c>
       <c r="K7" s="9">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="str">
+        <v>Tadka Dal (Red Lentil Curry) A flavorful and hearty dish, made with red lentils, simmered in mild spices, tempered with onions, garlic and cumin. Served with saffron flavored basmati rice &amp; Poppadum</v>
+      </c>
+      <c r="M7" s="9">
         <v>2</v>
-      </c>
-      <c r="L7" s="7" t="str">
-        <v>Beer battered Cod &amp; Chips served with chips, mushy peas, lemon wedge &amp; tartare sauce</v>
-      </c>
-      <c r="M7" s="9">
-        <v>8</v>
       </c>
       <c r="N7" s="7" t="str">
         <v>Cheesecake with Mix Berries Compote</v>
@@ -3106,7 +3093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
@@ -3117,28 +3104,24 @@
         <v>41</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="7" t="str">
-        <v>Lightly fried whitebait served with burnt lemon &amp; tartar dip</v>
-      </c>
-      <c r="K8" s="9">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="7" t="str">
-        <v>Tadka Dal (Red Lentil Curry) A flavorful and hearty dish, made with red lentils, simmered in mild spices, tempered with onions, garlic and cumin. Served with saffron flavored basmati rice &amp; Poppadum</v>
+        <v>Seafood Tagliatelle simmered in Bisque with prawns, squids &amp; mussels served with lemon, Urfa Chilli, chives &amp; Parmesan</v>
       </c>
       <c r="M8" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="9"/>
@@ -3152,10 +3135,10 @@
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>3</v>
@@ -3164,10 +3147,10 @@
       <c r="J9" s="7"/>
       <c r="K9" s="9"/>
       <c r="L9" s="7" t="str">
-        <v>Seafood Tagliatelle simmered in Bisque with prawns, squids &amp; mussels served with lemon, Urfa Chilli, chives &amp; Parmesan</v>
+        <v>Butter chicken in a rich &amp; silky makhani sauce served with saffron flavored basmati rice &amp; poppadum</v>
       </c>
       <c r="M9" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="9"/>
@@ -3184,20 +3167,16 @@
         <v>10</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H10" s="17"/>
       <c r="J10" s="7"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="7" t="str">
-        <v>Butter chicken in a rich &amp; silky makhani sauce served with saffron flavored basmati rice &amp; poppadum</v>
-      </c>
-      <c r="M10" s="9">
-        <v>2</v>
-      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="9"/>
       <c r="N10" s="7"/>
       <c r="O10" s="9"/>
     </row>
@@ -3213,10 +3192,10 @@
         <v>10</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H11" s="17"/>
       <c r="J11" s="7"/>
@@ -3238,10 +3217,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H12" s="17"/>
       <c r="J12" s="7"/>
@@ -3260,13 +3239,13 @@
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H13" s="17"/>
       <c r="J13" s="7"/>
@@ -3288,13 +3267,13 @@
         <v>10</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>57</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="9"/>
@@ -3315,10 +3294,10 @@
         <v>10</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H15" s="17"/>
       <c r="J15" s="7"/>
@@ -3337,10 +3316,10 @@
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>3</v>
@@ -3362,10 +3341,10 @@
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>3</v>
@@ -3390,10 +3369,10 @@
         <v>10</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H18" s="17"/>
       <c r="J18" s="2"/>
@@ -3405,7 +3384,7 @@
     </row>
     <row r="19" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>39</v>
@@ -3415,10 +3394,10 @@
         <v>10</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="17"/>
       <c r="J19" s="2"/>
@@ -3430,7 +3409,7 @@
     </row>
     <row r="20" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>39</v>
@@ -3440,13 +3419,13 @@
         <v>10</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="10"/>
@@ -3457,7 +3436,7 @@
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>39</v>
@@ -3467,31 +3446,31 @@
         <v>10</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H21" s="17"/>
     </row>
     <row r="22" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3595,7 +3574,7 @@
   <sheetData>
     <row r="1" spans="2:16" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C1" s="3"/>
     </row>
@@ -3626,7 +3605,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>31</v>
@@ -3662,14 +3641,14 @@
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I6" s="24"/>
       <c r="K6" s="7" t="str" cm="1">
@@ -3721,11 +3700,11 @@
         <v>10</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G7" s="24"/>
       <c r="H7" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I7" s="24"/>
       <c r="K7" s="7" t="str">
@@ -3761,10 +3740,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>3</v>
@@ -3798,10 +3777,10 @@
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G9" s="24"/>
       <c r="H9" s="23" t="s">
@@ -3832,10 +3811,10 @@
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="25" t="s">
@@ -3865,11 +3844,11 @@
         <v>10</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I11" s="26"/>
       <c r="K11" s="7"/>
@@ -3895,11 +3874,11 @@
         <v>10</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I12" s="26"/>
       <c r="K12" s="7"/>
@@ -3922,10 +3901,10 @@
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="25" t="s">
@@ -3952,14 +3931,14 @@
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I14" s="26"/>
       <c r="K14" s="7"/>
@@ -3985,7 +3964,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="25" t="s">
@@ -4012,10 +3991,10 @@
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="25" t="s">
@@ -4042,10 +4021,10 @@
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="25" t="s">
@@ -4068,10 +4047,10 @@
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="25" t="s">
@@ -4087,7 +4066,7 @@
     </row>
     <row r="19" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B19" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>39</v>
@@ -4097,11 +4076,11 @@
         <v>10</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I19" s="26"/>
       <c r="K19" s="2"/>
@@ -4113,7 +4092,7 @@
     </row>
     <row r="20" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B20" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>39</v>
@@ -4123,14 +4102,14 @@
         <v>10</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="25" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="10"/>
@@ -4141,7 +4120,7 @@
     </row>
     <row r="21" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B21" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>39</v>
@@ -4151,7 +4130,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21" s="26"/>
       <c r="H21" s="25" t="s">
@@ -4161,26 +4140,26 @@
     </row>
     <row r="22" spans="2:17" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B22" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
@@ -4262,7 +4241,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="B1:Q40"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
@@ -4281,20 +4260,14 @@
     <col min="16" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29" t="s">
-        <v>102</v>
+    <row r="1" spans="2:16" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B1" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-    </row>
-    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30" t="s">
+    <row r="3" spans="2:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="4"/>
@@ -4303,11 +4276,7 @@
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-    </row>
-    <row r="5" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="20" t="s">
         <v>33</v>
       </c>
@@ -4324,7 +4293,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>31</v>
@@ -4351,7 +4320,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>0</v>
       </c>
@@ -4360,10 +4329,10 @@
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="23" t="s">
@@ -4407,7 +4376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
         <v>16</v>
       </c>
@@ -4419,11 +4388,11 @@
         <v>10</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G7" s="24"/>
       <c r="H7" s="23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I7" s="24"/>
       <c r="K7" s="7" t="str">
@@ -4445,7 +4414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="15" t="s">
         <v>27</v>
       </c>
@@ -4456,19 +4425,19 @@
         <v>41</v>
       </c>
       <c r="E8" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>78</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>80</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>3</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K8" s="7" t="str">
         <v>Pheasant &amp; Mushroom Pate - With toasted sourdough - £8.95</v>
@@ -4489,7 +4458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
         <v>4</v>
       </c>
@@ -4498,16 +4467,16 @@
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="H9" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>85</v>
       </c>
       <c r="I9" s="24"/>
       <c r="K9" s="7" t="str">
@@ -4529,7 +4498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
         <v>19</v>
       </c>
@@ -4538,14 +4507,14 @@
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I10" s="26"/>
       <c r="K10" s="7" t="str">
@@ -4567,7 +4536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
@@ -4579,11 +4548,11 @@
         <v>10</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" s="26"/>
       <c r="K11" s="7" t="str">
@@ -4605,7 +4574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
@@ -4617,11 +4586,11 @@
         <v>10</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I12" s="26"/>
       <c r="K12" s="7" t="str">
@@ -4639,7 +4608,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="9"/>
     </row>
-    <row r="13" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B13" s="15" t="s">
         <v>7</v>
       </c>
@@ -4648,13 +4617,13 @@
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H13" s="25" t="s">
         <v>3</v>
@@ -4671,7 +4640,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="9"/>
     </row>
-    <row r="14" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="15" t="s">
         <v>21</v>
       </c>
@@ -4680,16 +4649,16 @@
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="25" t="s">
-        <v>76</v>
-      </c>
       <c r="G14" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I14" s="26"/>
       <c r="K14" s="7"/>
@@ -4703,7 +4672,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
         <v>42</v>
       </c>
@@ -4715,11 +4684,11 @@
         <v>10</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I15" s="26"/>
       <c r="K15" s="7"/>
@@ -4733,7 +4702,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="9"/>
     </row>
-    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="15" t="s">
         <v>24</v>
       </c>
@@ -4742,16 +4711,16 @@
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="H16" s="25" t="s">
         <v>96</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="I16" s="26"/>
       <c r="K16" s="7"/>
@@ -4777,10 +4746,10 @@
         <v>10</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H17" s="25" t="s">
         <v>3</v>
@@ -4806,14 +4775,14 @@
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I18" s="26"/>
       <c r="K18" s="2"/>
@@ -4825,7 +4794,7 @@
     </row>
     <row r="19" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B19" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>39</v>
@@ -4835,11 +4804,11 @@
         <v>10</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I19" s="26"/>
       <c r="K19" s="2"/>
@@ -4851,7 +4820,7 @@
     </row>
     <row r="20" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B20" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>39</v>
@@ -4861,14 +4830,14 @@
         <v>10</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="10"/>
@@ -4879,45 +4848,45 @@
     </row>
     <row r="21" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B21" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G21" s="26"/>
       <c r="H21" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B22" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I22" s="26"/>
     </row>

--- a/files/Menus Listed.xlsx
+++ b/files/Menus Listed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb03e65629f95fa6/Documents/01 Personal/01 Web Development/01 Sites/11 C2C Rides/C2C_Rides/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{828D102A-55D7-4261-93B7-DF7B56032332}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C3A3A1-1D16-4EF8-97BA-FC3CB537B168}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
   </bookViews>
   <sheets>
     <sheet name="Hotel 1 - Menu Info" sheetId="5" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="123">
   <si>
     <t>David Olney</t>
   </si>
@@ -430,6 +430,12 @@
   </si>
   <si>
     <t>Leek, Mushroom &amp; Lentil Shepherds Pie (VG) - With mashed potato and vegetables - £16.95</t>
+  </si>
+  <si>
+    <t>Carole Griffiths</t>
+  </si>
+  <si>
+    <t>Ham &amp; Leek Pie with mash, sticky red cabbage, gravy - £17.50</t>
   </si>
 </sst>
 </file>
@@ -746,6 +752,296 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="0"/>
         </patternFill>
@@ -1036,6 +1332,257 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
@@ -1290,547 +1837,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1849,7 +1855,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:H24" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BDC5DD8C-8F3E-4BEC-A03C-C59C0B228BFD}" name="tblHotel13" displayName="tblHotel13" ref="B5:H24" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
   <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1860,20 +1866,20 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{E6C72533-73F5-43F8-B0CD-008DE01142AB}" name="Meal preparation comments" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{5C92B494-EA13-4F74-8319-EBAE3BE04F45}" name="Name" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{9B701A91-19E7-4848-B56A-34A87B459979}" name="Special Dietry" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{6D4EFF28-A45C-451C-B654-FA02BA4A9C8C}" name="Dietary Requirements" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{15CFB543-AC2D-4314-9767-3B81465700E3}" name="Starter" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{013D16B1-5ADC-40B7-BE1E-1571006023A7}" name="Main" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{47CF3618-1C78-4C3D-A65A-A414EECFA4C6}" name="Dessert" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{E6C72533-73F5-43F8-B0CD-008DE01142AB}" name="Meal preparation comments" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H24" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{950745C7-633F-4D36-9314-308A644252A9}" name="tblHotel134" displayName="tblHotel134" ref="B5:H24" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="B5:H24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1884,20 +1890,20 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E5B23A81-8537-439C-92B6-0B5779C8DF6A}" name="Name" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{03AC1E81-4707-45B6-B2BF-1066B19ACDF8}" name="Special Dietry" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{1B5B102A-80ED-4B8D-BE1F-8E0BB65E53ED}" name="Dietary Requirements" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{1AA91233-FC32-4D76-9572-95850514AD4B}" name="Starter" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{EF744B57-EB73-45FE-B267-F484F45B84E9}" name="Main" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{0C2C717A-4D81-48D0-831C-E992206553F1}" name="Dessert" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{4B5E53FF-F7B4-44F2-9E2E-AC4A8095BDFE}" name="Meal preparation comments" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I24" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4E7A2A2-BB86-4BEB-AC00-2AE478EA77AC}" name="tblHotel1345" displayName="tblHotel1345" ref="B5:I24" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1909,21 +1915,21 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DD6DF8E8-5F13-493F-966A-EE048DF204DA}" name="Name" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{CD31701D-787B-40B6-A3AC-06283F21D5D1}" name="Special Dietry" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{6B466A34-5276-432A-A354-229ECBDC5F79}" name="Dietary Requirements" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{0D215AE5-9BB5-4170-BE58-0731DF8AA5AD}" name="Starter" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{E9B4E8C3-8ED7-4E70-B344-F41FE1183D6E}" name="Main" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{061D587E-3BD7-4313-AC94-8D39339D2BDA}" name="Side dishes / steak sauce" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{AA588DA8-6E33-4E29-BC42-468EEC3EC734}" name="Dessert" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{A154A397-195F-4C28-9DFA-BC7735B077AA}" name="Meal preparation comments" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I24" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{178C68DD-EC88-4B55-B847-28BD02EF2F85}" name="tblHotel13456" displayName="tblHotel13456" ref="B5:I24" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="B5:I24" xr:uid="{929BF493-60F1-4568-9C13-C8AE0F2D6B21}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1935,14 +1941,14 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{6701036E-A63F-4B9D-A97A-92DE794C92BE}" name="Name" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{23AE8140-BC17-42BB-A45F-056750FF7CA0}" name="Special Dietry" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B13D55E2-E4D7-4532-B0A8-6EDAE6C17216}" name="Dietary Requirements" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9E046FD6-3D86-4701-8393-0BB732B6D664}" name="Starter" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00D04535-5BE5-4D3D-A9E2-5556A7545B1C}" name="Main" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{51F31383-DCF3-493D-8997-69FA6F6EA44D}" name="Side dishes / steak sauce" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{FB576E1F-59CC-4680-A437-5A52CEB90C07}" name="Dessert" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{4FF16550-030B-4358-AEF8-58E5137FA553}" name="Meal preparation comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2377,7 +2383,7 @@
         <v>4</v>
       </c>
       <c r="L6" s="7" t="str" cm="1">
-        <f t="array" ref="L6:M14">_xlfn.LET(
+        <f t="array" ref="L6:M15">_xlfn.LET(
     _xlpm.rng, tblHotel13[Main],
     _xlpm.u, _xlfn.UNIQUE(_xlpm.rng),
     _xlpm.uClean, _xlfn._xlws.FILTER(_xlpm.u, (_xlpm.u &lt;&gt; "No Main") * (_xlpm.u &lt;&gt; "")),
@@ -2675,8 +2681,12 @@
       <c r="H15" s="16"/>
       <c r="J15" s="7"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="L15" s="7" t="str">
+        <v>Ham &amp; Leek Pie with mash, sticky red cabbage, gravy - £17.50</v>
+      </c>
+      <c r="M15" s="9">
+        <v>1</v>
+      </c>
       <c r="N15" s="7"/>
       <c r="O15" s="9"/>
     </row>
@@ -2846,12 +2856,22 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
+      <c r="B23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
+      <c r="E23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
@@ -3039,7 +3059,7 @@
         <v>Beer battered Cod &amp; Chips served with chips, mushy peas, lemon wedge &amp; tartare sauce</v>
       </c>
       <c r="M6" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" s="7" t="str" cm="1">
         <f t="array" ref="N6:O7">_xlfn.LET(
@@ -3051,7 +3071,7 @@
         <v>Sticky Toffee Pudding with Custard</v>
       </c>
       <c r="O6" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
@@ -3093,7 +3113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
@@ -3474,13 +3494,23 @@
       </c>
       <c r="H22" s="17"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
+    <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
+      <c r="E23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="H23" s="17"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
@@ -3793,7 +3823,7 @@
         <v>Classic Dishes: Nanhoron Tikka Curry - Chicken, Served with rice, naan, mango chutney - £15.95</v>
       </c>
       <c r="N9" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="7" t="str">
         <v>Double Chocolate Brownie - Warm Brownie served with signature chocolate sauce &amp; vanilla ice cream - £7.95</v>
@@ -4162,14 +4192,24 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+    <row r="23" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="E23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>65</v>
+      </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="I23" s="15"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
@@ -4495,7 +4535,7 @@
         <v>Rhubarb &amp; Stem Ginger Crumble (V) - With vanilla ice cream - £7.95</v>
       </c>
       <c r="P9" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -4729,7 +4769,7 @@
         <v>Cumberland Sausage &amp; Mash - With vegetables and gravy - £17.95</v>
       </c>
       <c r="N16" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="9"/>
@@ -4890,14 +4930,24 @@
       </c>
       <c r="I22" s="26"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+    <row r="23" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="E23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
